--- a/MDA/demo_mda_9999_2_part.xlsx
+++ b/MDA/demo_mda_9999_2_part.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5515B2F-F253-4C6D-8823-22BA5034A6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F58902-EB49-4119-A862-82475620E739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,15 +371,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -389,31 +395,16 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.14990691854609822"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.14990691854609822"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.14990691854609822"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.14990691854609822"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -424,15 +415,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -440,25 +428,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -742,396 +744,699 @@
   <dimension ref="A1:U20"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="24.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.25" style="6" customWidth="1"/>
-    <col min="3" max="3" width="42.625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="41.25" style="6" customWidth="1"/>
-    <col min="5" max="5" width="12.625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="25.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="29.5" style="6" customWidth="1"/>
-    <col min="8" max="8" width="17.875" style="6" customWidth="1"/>
-    <col min="9" max="9" width="19.625" style="6" customWidth="1"/>
-    <col min="10" max="10" width="9.75" style="6" customWidth="1"/>
-    <col min="11" max="11" width="20.625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="9.125" style="6" customWidth="1"/>
-    <col min="13" max="13" width="20.5" style="6" customWidth="1"/>
-    <col min="14" max="15" width="11" style="6"/>
-    <col min="16" max="16" width="11.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="22.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11" style="6"/>
+    <col min="1" max="1" width="24.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.25" style="5" customWidth="1"/>
+    <col min="3" max="3" width="42.625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="41.25" style="5" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12" style="5" customWidth="1"/>
+    <col min="7" max="7" width="29.5" style="5" customWidth="1"/>
+    <col min="8" max="8" width="17.875" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="9.75" style="5" customWidth="1"/>
+    <col min="11" max="11" width="20.625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="9.125" style="5" customWidth="1"/>
+    <col min="13" max="13" width="20.5" style="5" customWidth="1"/>
+    <col min="14" max="15" width="11" style="5"/>
+    <col min="16" max="16" width="11.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="22.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="18" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" ht="31.5">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="31.5">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="T1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="U1" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:21" s="4" customFormat="1">
+      <c r="A2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="3"/>
-      <c r="J2" s="4" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="13" t="s">
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="9" t="s">
         <v>84</v>
       </c>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9" t="s">
         <v>85</v>
       </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9" t="s">
         <v>85</v>
       </c>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="D7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="D9" s="10"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="D10" s="10"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="I11" s="9"/>
+      <c r="J11" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="I12" s="9"/>
+      <c r="J12" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="D13" s="10"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="I13" s="9"/>
+      <c r="J13" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="D14" s="10"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="I14" s="9"/>
+      <c r="J14" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="D15" s="10"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="I15" s="9"/>
+      <c r="J15" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="D16" s="10"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="I16" s="9"/>
+      <c r="J16" s="8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="6" t="s">
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="D17" s="10"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="I17" s="9"/>
+      <c r="J17" s="8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="6" t="s">
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="D18" s="10"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="6" t="s">
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="6" t="s">
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="9" t="s">
         <v>21</v>
       </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -1145,47 +1450,47 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="14.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="23.75" style="6" customWidth="1"/>
-    <col min="4" max="16384" width="11" style="6"/>
+    <col min="1" max="1" width="14.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="23.75" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="4"/>
+      <c r="A4" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:C30">
@@ -1217,10 +1522,10 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C2" t="s">

--- a/MDA/demo_mda_9999_2_part.xlsx
+++ b/MDA/demo_mda_9999_2_part.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F58902-EB49-4119-A862-82475620E739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCEA6B2-D971-4195-B02F-A1F8A73F649D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="89">
   <si>
     <t>type</t>
   </si>
@@ -296,6 +296,12 @@
   </si>
   <si>
     <t>Total Tetracycline received</t>
+  </si>
+  <si>
+    <t>p_total_az_tab</t>
+  </si>
+  <si>
+    <t>Total Azithromycin tablets received</t>
   </si>
 </sst>
 </file>
@@ -741,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="24.25" style="5" bestFit="1" customWidth="1"/>
@@ -1325,10 +1331,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="9"/>
@@ -1355,22 +1361,24 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="9"/>
+      <c r="H18" s="9" t="s">
+        <v>83</v>
+      </c>
       <c r="I18" s="9"/>
       <c r="J18" s="8" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
@@ -1386,19 +1394,23 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="D19" s="10"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="10"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="J19" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
@@ -1413,10 +1425,10 @@
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -1437,6 +1449,33 @@
       <c r="S20" s="9"/>
       <c r="T20" s="9"/>
       <c r="U20" s="9"/>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
